--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,2377 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>113701690</v>
+      </c>
+      <c r="B3" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>760880</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7168494</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>113701658</v>
+      </c>
+      <c r="B4" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>761076</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7168434</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113701680</v>
+      </c>
+      <c r="B5" t="n">
+        <v>77604</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>760943</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7168426</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>113701664</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>760841</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7168507</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>113701685</v>
+      </c>
+      <c r="B7" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760979</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7168521</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113701678</v>
+      </c>
+      <c r="B8" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760891</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7168581</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>113701703</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760853</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7168609</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113701687</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90150</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760931</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7168515</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113701702</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760873</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7168557</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>113701679</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90150</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760876</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7168516</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>113701689</v>
+      </c>
+      <c r="B13" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>760901</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7168493</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113701701</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>760835</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7168525</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113701659</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56826</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>760985</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7168527</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>113701683</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>761010</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7168418</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113701700</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>760847</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7168462</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113701682</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79199</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>761040</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7168409</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113701684</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>760985</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7168457</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>113701663</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90150</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>760896</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7168483</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113701681</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>761131</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7168392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113701686</v>
+      </c>
+      <c r="B22" t="n">
+        <v>81944</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>760976</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7168520</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>113701662</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78201</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>760965</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7168517</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>113701688</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56917</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dalfors, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>760924</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7168506</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2023-10-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>SWECO Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elias Forsberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701690</v>
+        <v>113701663</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>90151</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760880</v>
+        <v>760896</v>
       </c>
       <c r="R3" t="n">
-        <v>7168494</v>
+        <v>7168483</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701658</v>
+        <v>113701688</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>56917</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +906,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761076</v>
+        <v>760924</v>
       </c>
       <c r="R4" t="n">
-        <v>7168434</v>
+        <v>7168506</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701680</v>
+        <v>113701682</v>
       </c>
       <c r="B5" t="n">
-        <v>77604</v>
+        <v>79199</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,25 +1025,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1053,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760943</v>
+        <v>761040</v>
       </c>
       <c r="R5" t="n">
-        <v>7168426</v>
+        <v>7168409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701664</v>
+        <v>113701689</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1136,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760841</v>
+        <v>760901</v>
       </c>
       <c r="R6" t="n">
-        <v>7168507</v>
+        <v>7168493</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1227,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701685</v>
+        <v>113701679</v>
       </c>
       <c r="B7" t="n">
-        <v>81944</v>
+        <v>90151</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1243,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1267,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760979</v>
+        <v>760876</v>
       </c>
       <c r="R7" t="n">
-        <v>7168521</v>
+        <v>7168516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701678</v>
+        <v>113701703</v>
       </c>
       <c r="B8" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,21 +1350,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760891</v>
+        <v>760853</v>
       </c>
       <c r="R8" t="n">
-        <v>7168581</v>
+        <v>7168609</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113701703</v>
+        <v>113701685</v>
       </c>
       <c r="B9" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1445,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760853</v>
+        <v>760979</v>
       </c>
       <c r="R9" t="n">
-        <v>7168609</v>
+        <v>7168521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1539,7 +1551,7 @@
         <v>113701687</v>
       </c>
       <c r="B10" t="n">
-        <v>90150</v>
+        <v>90151</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,7 +1655,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701702</v>
+        <v>113701684</v>
       </c>
       <c r="B11" t="n">
         <v>78201</v>
@@ -1683,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760873</v>
+        <v>760985</v>
       </c>
       <c r="R11" t="n">
-        <v>7168557</v>
+        <v>7168457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701679</v>
+        <v>113701683</v>
       </c>
       <c r="B12" t="n">
-        <v>90150</v>
+        <v>78201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1778,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760876</v>
+        <v>761010</v>
       </c>
       <c r="R12" t="n">
-        <v>7168516</v>
+        <v>7168418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113701689</v>
+        <v>113701700</v>
       </c>
       <c r="B13" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760901</v>
+        <v>760847</v>
       </c>
       <c r="R13" t="n">
-        <v>7168493</v>
+        <v>7168462</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1976,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113701701</v>
+        <v>113701686</v>
       </c>
       <c r="B14" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1992,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760835</v>
+        <v>760976</v>
       </c>
       <c r="R14" t="n">
-        <v>7168525</v>
+        <v>7168520</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113701659</v>
+        <v>113701690</v>
       </c>
       <c r="B15" t="n">
-        <v>56826</v>
+        <v>81944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,39 +2099,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760985</v>
+        <v>760880</v>
       </c>
       <c r="R15" t="n">
-        <v>7168527</v>
+        <v>7168494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2190,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113701683</v>
+        <v>113701659</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>56826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,34 +2206,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761010</v>
+        <v>760985</v>
       </c>
       <c r="R16" t="n">
-        <v>7168418</v>
+        <v>7168527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113701700</v>
+        <v>113701662</v>
       </c>
       <c r="B17" t="n">
         <v>78201</v>
@@ -2330,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>760847</v>
+        <v>760965</v>
       </c>
       <c r="R17" t="n">
-        <v>7168462</v>
+        <v>7168517</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701682</v>
+        <v>113701658</v>
       </c>
       <c r="B18" t="n">
-        <v>79199</v>
+        <v>81944</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,25 +2421,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761040</v>
+        <v>761076</v>
       </c>
       <c r="R18" t="n">
-        <v>7168409</v>
+        <v>7168434</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701684</v>
+        <v>113701680</v>
       </c>
       <c r="B19" t="n">
-        <v>78201</v>
+        <v>77604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2532,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760985</v>
+        <v>760943</v>
       </c>
       <c r="R19" t="n">
-        <v>7168457</v>
+        <v>7168426</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113701663</v>
+        <v>113701702</v>
       </c>
       <c r="B20" t="n">
-        <v>90150</v>
+        <v>78201</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760896</v>
+        <v>760873</v>
       </c>
       <c r="R20" t="n">
-        <v>7168483</v>
+        <v>7168557</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,7 +2730,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113701681</v>
+        <v>113701664</v>
       </c>
       <c r="B21" t="n">
         <v>78201</v>
@@ -2758,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>761131</v>
+        <v>760841</v>
       </c>
       <c r="R21" t="n">
-        <v>7168392</v>
+        <v>7168507</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,7 +2837,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113701686</v>
+        <v>113701678</v>
       </c>
       <c r="B22" t="n">
         <v>81944</v>
@@ -2865,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760976</v>
+        <v>760891</v>
       </c>
       <c r="R22" t="n">
-        <v>7168520</v>
+        <v>7168581</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,7 +2944,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113701662</v>
+        <v>113701701</v>
       </c>
       <c r="B23" t="n">
         <v>78201</v>
@@ -2972,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760965</v>
+        <v>760835</v>
       </c>
       <c r="R23" t="n">
-        <v>7168517</v>
+        <v>7168525</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3039,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113701688</v>
+        <v>113701681</v>
       </c>
       <c r="B24" t="n">
-        <v>56917</v>
+        <v>78201</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3051,50 +3063,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>760924</v>
+        <v>761131</v>
       </c>
       <c r="R24" t="n">
-        <v>7168506</v>
+        <v>7168392</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701663</v>
+        <v>113701690</v>
       </c>
       <c r="B3" t="n">
-        <v>90151</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760896</v>
+        <v>760880</v>
       </c>
       <c r="R3" t="n">
-        <v>7168483</v>
+        <v>7168494</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701688</v>
+        <v>113701685</v>
       </c>
       <c r="B4" t="n">
-        <v>56917</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,50 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760924</v>
+        <v>760979</v>
       </c>
       <c r="R4" t="n">
-        <v>7168506</v>
+        <v>7168521</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701682</v>
+        <v>113701680</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>77604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1053,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761040</v>
+        <v>760943</v>
       </c>
       <c r="R5" t="n">
-        <v>7168409</v>
+        <v>7168426</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701689</v>
+        <v>113701678</v>
       </c>
       <c r="B6" t="n">
         <v>81944</v>
@@ -1160,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760901</v>
+        <v>760891</v>
       </c>
       <c r="R6" t="n">
-        <v>7168493</v>
+        <v>7168581</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701679</v>
+        <v>113701683</v>
       </c>
       <c r="B7" t="n">
-        <v>90151</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1267,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760876</v>
+        <v>761010</v>
       </c>
       <c r="R7" t="n">
-        <v>7168516</v>
+        <v>7168418</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701703</v>
+        <v>113701679</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760853</v>
+        <v>760876</v>
       </c>
       <c r="R8" t="n">
-        <v>7168609</v>
+        <v>7168516</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113701685</v>
+        <v>113701682</v>
       </c>
       <c r="B9" t="n">
-        <v>81944</v>
+        <v>79199</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,25 +1441,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760979</v>
+        <v>761040</v>
       </c>
       <c r="R9" t="n">
-        <v>7168521</v>
+        <v>7168409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113701687</v>
+        <v>113701681</v>
       </c>
       <c r="B10" t="n">
-        <v>90151</v>
+        <v>78201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760931</v>
+        <v>761131</v>
       </c>
       <c r="R10" t="n">
-        <v>7168515</v>
+        <v>7168392</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,10 +1643,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701684</v>
+        <v>113701659</v>
       </c>
       <c r="B11" t="n">
-        <v>78201</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,24 +1659,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
@@ -1698,7 +1691,7 @@
         <v>760985</v>
       </c>
       <c r="R11" t="n">
-        <v>7168457</v>
+        <v>7168527</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701683</v>
+        <v>113701686</v>
       </c>
       <c r="B12" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1778,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1802,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761010</v>
+        <v>760976</v>
       </c>
       <c r="R12" t="n">
-        <v>7168418</v>
+        <v>7168520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113701700</v>
+        <v>113701689</v>
       </c>
       <c r="B13" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760847</v>
+        <v>760901</v>
       </c>
       <c r="R13" t="n">
-        <v>7168462</v>
+        <v>7168493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113701686</v>
+        <v>113701662</v>
       </c>
       <c r="B14" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1992,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2016,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760976</v>
+        <v>760965</v>
       </c>
       <c r="R14" t="n">
-        <v>7168520</v>
+        <v>7168517</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113701690</v>
+        <v>113701702</v>
       </c>
       <c r="B15" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2123,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760880</v>
+        <v>760873</v>
       </c>
       <c r="R15" t="n">
-        <v>7168494</v>
+        <v>7168557</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2190,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113701659</v>
+        <v>113701658</v>
       </c>
       <c r="B16" t="n">
-        <v>56826</v>
+        <v>81944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,39 +2199,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760985</v>
+        <v>761076</v>
       </c>
       <c r="R16" t="n">
-        <v>7168527</v>
+        <v>7168434</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,7 +2290,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113701662</v>
+        <v>113701700</v>
       </c>
       <c r="B17" t="n">
         <v>78201</v>
@@ -2342,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>760965</v>
+        <v>760847</v>
       </c>
       <c r="R17" t="n">
-        <v>7168517</v>
+        <v>7168462</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701658</v>
+        <v>113701663</v>
       </c>
       <c r="B18" t="n">
-        <v>81944</v>
+        <v>90155</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,21 +2413,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2449,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761076</v>
+        <v>760896</v>
       </c>
       <c r="R18" t="n">
-        <v>7168434</v>
+        <v>7168483</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701680</v>
+        <v>113701687</v>
       </c>
       <c r="B19" t="n">
-        <v>77604</v>
+        <v>90155</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2556,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760943</v>
+        <v>760931</v>
       </c>
       <c r="R19" t="n">
-        <v>7168426</v>
+        <v>7168515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2611,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113701702</v>
+        <v>113701664</v>
       </c>
       <c r="B20" t="n">
         <v>78201</v>
@@ -2663,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760873</v>
+        <v>760841</v>
       </c>
       <c r="R20" t="n">
-        <v>7168557</v>
+        <v>7168507</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113701664</v>
+        <v>113701688</v>
       </c>
       <c r="B21" t="n">
-        <v>78201</v>
+        <v>56917</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2742,38 +2730,50 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>760841</v>
+        <v>760924</v>
       </c>
       <c r="R21" t="n">
-        <v>7168507</v>
+        <v>7168506</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113701678</v>
+        <v>113701684</v>
       </c>
       <c r="B22" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760891</v>
+        <v>760985</v>
       </c>
       <c r="R22" t="n">
-        <v>7168581</v>
+        <v>7168457</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113701701</v>
+        <v>113701703</v>
       </c>
       <c r="B23" t="n">
         <v>78201</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760835</v>
+        <v>760853</v>
       </c>
       <c r="R23" t="n">
-        <v>7168525</v>
+        <v>7168609</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113701681</v>
+        <v>113701701</v>
       </c>
       <c r="B24" t="n">
         <v>78201</v>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>761131</v>
+        <v>760835</v>
       </c>
       <c r="R24" t="n">
-        <v>7168392</v>
+        <v>7168525</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701690</v>
+        <v>113701687</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>90155</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760880</v>
+        <v>760931</v>
       </c>
       <c r="R3" t="n">
-        <v>7168494</v>
+        <v>7168515</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701685</v>
+        <v>113701700</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760979</v>
+        <v>760847</v>
       </c>
       <c r="R4" t="n">
-        <v>7168521</v>
+        <v>7168462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701680</v>
+        <v>113701664</v>
       </c>
       <c r="B5" t="n">
-        <v>77604</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760943</v>
+        <v>760841</v>
       </c>
       <c r="R5" t="n">
-        <v>7168426</v>
+        <v>7168507</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701678</v>
+        <v>113701686</v>
       </c>
       <c r="B6" t="n">
         <v>81944</v>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760891</v>
+        <v>760976</v>
       </c>
       <c r="R6" t="n">
-        <v>7168581</v>
+        <v>7168520</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701683</v>
+        <v>113701678</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>761010</v>
+        <v>760891</v>
       </c>
       <c r="R7" t="n">
-        <v>7168418</v>
+        <v>7168581</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701679</v>
+        <v>113701659</v>
       </c>
       <c r="B8" t="n">
-        <v>90155</v>
+        <v>56826</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,34 +1338,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760876</v>
+        <v>760985</v>
       </c>
       <c r="R8" t="n">
-        <v>7168516</v>
+        <v>7168527</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113701682</v>
+        <v>113701663</v>
       </c>
       <c r="B9" t="n">
-        <v>79199</v>
+        <v>90155</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1474,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761040</v>
+        <v>760896</v>
       </c>
       <c r="R9" t="n">
-        <v>7168409</v>
+        <v>7168483</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113701681</v>
+        <v>113701679</v>
       </c>
       <c r="B10" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,21 +1557,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1581,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761131</v>
+        <v>760876</v>
       </c>
       <c r="R10" t="n">
-        <v>7168392</v>
+        <v>7168516</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701659</v>
+        <v>113701658</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>81944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,39 +1664,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760985</v>
+        <v>761076</v>
       </c>
       <c r="R11" t="n">
-        <v>7168527</v>
+        <v>7168434</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701686</v>
+        <v>113701689</v>
       </c>
       <c r="B12" t="n">
         <v>81944</v>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760976</v>
+        <v>760901</v>
       </c>
       <c r="R12" t="n">
-        <v>7168520</v>
+        <v>7168493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113701689</v>
+        <v>113701684</v>
       </c>
       <c r="B13" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760901</v>
+        <v>760985</v>
       </c>
       <c r="R13" t="n">
-        <v>7168493</v>
+        <v>7168457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1969,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113701662</v>
+        <v>113701681</v>
       </c>
       <c r="B14" t="n">
         <v>78201</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760965</v>
+        <v>761131</v>
       </c>
       <c r="R14" t="n">
-        <v>7168517</v>
+        <v>7168392</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113701702</v>
+        <v>113701701</v>
       </c>
       <c r="B15" t="n">
         <v>78201</v>
@@ -2116,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760873</v>
+        <v>760835</v>
       </c>
       <c r="R15" t="n">
-        <v>7168557</v>
+        <v>7168525</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113701658</v>
+        <v>113701683</v>
       </c>
       <c r="B16" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761076</v>
+        <v>761010</v>
       </c>
       <c r="R16" t="n">
-        <v>7168434</v>
+        <v>7168418</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113701700</v>
+        <v>113701690</v>
       </c>
       <c r="B17" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>760847</v>
+        <v>760880</v>
       </c>
       <c r="R17" t="n">
-        <v>7168462</v>
+        <v>7168494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701663</v>
+        <v>113701682</v>
       </c>
       <c r="B18" t="n">
-        <v>90155</v>
+        <v>79199</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,25 +2409,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760896</v>
+        <v>761040</v>
       </c>
       <c r="R18" t="n">
-        <v>7168483</v>
+        <v>7168409</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701687</v>
+        <v>113701688</v>
       </c>
       <c r="B19" t="n">
-        <v>90155</v>
+        <v>56917</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,38 +2516,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760931</v>
+        <v>760924</v>
       </c>
       <c r="R19" t="n">
-        <v>7168515</v>
+        <v>7168506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,7 +2623,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113701664</v>
+        <v>113701662</v>
       </c>
       <c r="B20" t="n">
         <v>78201</v>
@@ -2651,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760841</v>
+        <v>760965</v>
       </c>
       <c r="R20" t="n">
-        <v>7168507</v>
+        <v>7168517</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2730,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113701688</v>
+        <v>113701703</v>
       </c>
       <c r="B21" t="n">
-        <v>56917</v>
+        <v>78201</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2730,50 +2742,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>760924</v>
+        <v>760853</v>
       </c>
       <c r="R21" t="n">
-        <v>7168506</v>
+        <v>7168609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2837,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113701684</v>
+        <v>113701685</v>
       </c>
       <c r="B22" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2853,21 +2853,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760985</v>
+        <v>760979</v>
       </c>
       <c r="R22" t="n">
-        <v>7168457</v>
+        <v>7168521</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113701703</v>
+        <v>113701702</v>
       </c>
       <c r="B23" t="n">
         <v>78201</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760853</v>
+        <v>760873</v>
       </c>
       <c r="R23" t="n">
-        <v>7168609</v>
+        <v>7168557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113701701</v>
+        <v>113701680</v>
       </c>
       <c r="B24" t="n">
-        <v>78201</v>
+        <v>77604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>760835</v>
+        <v>760943</v>
       </c>
       <c r="R24" t="n">
-        <v>7168525</v>
+        <v>7168426</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701687</v>
+        <v>113701684</v>
       </c>
       <c r="B3" t="n">
-        <v>90155</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760931</v>
+        <v>760985</v>
       </c>
       <c r="R3" t="n">
-        <v>7168515</v>
+        <v>7168457</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701700</v>
+        <v>113701687</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760847</v>
+        <v>760931</v>
       </c>
       <c r="R4" t="n">
-        <v>7168462</v>
+        <v>7168515</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701664</v>
+        <v>113701686</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760841</v>
+        <v>760976</v>
       </c>
       <c r="R5" t="n">
-        <v>7168507</v>
+        <v>7168520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701686</v>
+        <v>113701682</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>79199</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760976</v>
+        <v>761040</v>
       </c>
       <c r="R6" t="n">
-        <v>7168520</v>
+        <v>7168409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701678</v>
+        <v>113701688</v>
       </c>
       <c r="B7" t="n">
-        <v>81944</v>
+        <v>56917</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,38 +1227,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760891</v>
+        <v>760924</v>
       </c>
       <c r="R7" t="n">
-        <v>7168581</v>
+        <v>7168506</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1334,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701659</v>
+        <v>113701683</v>
       </c>
       <c r="B8" t="n">
-        <v>56826</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,39 +1350,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760985</v>
+        <v>761010</v>
       </c>
       <c r="R8" t="n">
-        <v>7168527</v>
+        <v>7168418</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113701663</v>
+        <v>113701703</v>
       </c>
       <c r="B9" t="n">
-        <v>90155</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1450,21 +1457,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1474,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760896</v>
+        <v>760853</v>
       </c>
       <c r="R9" t="n">
-        <v>7168483</v>
+        <v>7168609</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113701679</v>
+        <v>113701689</v>
       </c>
       <c r="B10" t="n">
-        <v>90155</v>
+        <v>81944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,21 +1564,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760876</v>
+        <v>760901</v>
       </c>
       <c r="R10" t="n">
-        <v>7168516</v>
+        <v>7168493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1648,7 +1655,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701658</v>
+        <v>113701685</v>
       </c>
       <c r="B11" t="n">
         <v>81944</v>
@@ -1688,10 +1695,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>761076</v>
+        <v>760979</v>
       </c>
       <c r="R11" t="n">
-        <v>7168434</v>
+        <v>7168521</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1755,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701689</v>
+        <v>113701700</v>
       </c>
       <c r="B12" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1778,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1802,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760901</v>
+        <v>760847</v>
       </c>
       <c r="R12" t="n">
-        <v>7168493</v>
+        <v>7168462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1862,10 +1869,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113701684</v>
+        <v>113701680</v>
       </c>
       <c r="B13" t="n">
-        <v>78201</v>
+        <v>77604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1878,21 +1885,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1902,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760985</v>
+        <v>760943</v>
       </c>
       <c r="R13" t="n">
-        <v>7168457</v>
+        <v>7168426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1969,7 +1976,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113701681</v>
+        <v>113701662</v>
       </c>
       <c r="B14" t="n">
         <v>78201</v>
@@ -2009,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761131</v>
+        <v>760965</v>
       </c>
       <c r="R14" t="n">
-        <v>7168392</v>
+        <v>7168517</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2076,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113701701</v>
+        <v>113701659</v>
       </c>
       <c r="B15" t="n">
-        <v>78201</v>
+        <v>56826</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2092,34 +2099,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760835</v>
+        <v>760985</v>
       </c>
       <c r="R15" t="n">
-        <v>7168525</v>
+        <v>7168527</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2183,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113701683</v>
+        <v>113701679</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2199,21 +2211,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,10 +2235,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>761010</v>
+        <v>760876</v>
       </c>
       <c r="R16" t="n">
-        <v>7168418</v>
+        <v>7168516</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2290,7 +2302,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113701690</v>
+        <v>113701658</v>
       </c>
       <c r="B17" t="n">
         <v>81944</v>
@@ -2330,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>760880</v>
+        <v>761076</v>
       </c>
       <c r="R17" t="n">
-        <v>7168494</v>
+        <v>7168434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2397,10 +2409,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701682</v>
+        <v>113701664</v>
       </c>
       <c r="B18" t="n">
-        <v>79199</v>
+        <v>78201</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2409,25 +2421,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2437,10 +2449,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>761040</v>
+        <v>760841</v>
       </c>
       <c r="R18" t="n">
-        <v>7168409</v>
+        <v>7168507</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2516,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701688</v>
+        <v>113701678</v>
       </c>
       <c r="B19" t="n">
-        <v>56917</v>
+        <v>81944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,50 +2528,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760924</v>
+        <v>760891</v>
       </c>
       <c r="R19" t="n">
-        <v>7168506</v>
+        <v>7168581</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113701662</v>
+        <v>113701663</v>
       </c>
       <c r="B20" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2663,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760965</v>
+        <v>760896</v>
       </c>
       <c r="R20" t="n">
-        <v>7168517</v>
+        <v>7168483</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,7 +2730,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113701703</v>
+        <v>113701701</v>
       </c>
       <c r="B21" t="n">
         <v>78201</v>
@@ -2770,10 +2770,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>760853</v>
+        <v>760835</v>
       </c>
       <c r="R21" t="n">
-        <v>7168609</v>
+        <v>7168525</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113701685</v>
+        <v>113701690</v>
       </c>
       <c r="B22" t="n">
         <v>81944</v>
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760979</v>
+        <v>760880</v>
       </c>
       <c r="R22" t="n">
-        <v>7168521</v>
+        <v>7168494</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,7 +2944,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113701702</v>
+        <v>113701681</v>
       </c>
       <c r="B23" t="n">
         <v>78201</v>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>760873</v>
+        <v>761131</v>
       </c>
       <c r="R23" t="n">
-        <v>7168557</v>
+        <v>7168392</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113701680</v>
+        <v>113701702</v>
       </c>
       <c r="B24" t="n">
-        <v>77604</v>
+        <v>78201</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>760943</v>
+        <v>760873</v>
       </c>
       <c r="R24" t="n">
-        <v>7168426</v>
+        <v>7168557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701684</v>
+        <v>113701700</v>
       </c>
       <c r="B3" t="n">
         <v>78201</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760985</v>
+        <v>760847</v>
       </c>
       <c r="R3" t="n">
-        <v>7168457</v>
+        <v>7168462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701687</v>
+        <v>113701682</v>
       </c>
       <c r="B4" t="n">
-        <v>90155</v>
+        <v>79199</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760931</v>
+        <v>761040</v>
       </c>
       <c r="R4" t="n">
-        <v>7168515</v>
+        <v>7168409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701686</v>
+        <v>113701702</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760976</v>
+        <v>760873</v>
       </c>
       <c r="R5" t="n">
-        <v>7168520</v>
+        <v>7168557</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701682</v>
+        <v>113701658</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,25 +1120,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761040</v>
+        <v>761076</v>
       </c>
       <c r="R6" t="n">
-        <v>7168409</v>
+        <v>7168434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701688</v>
+        <v>113701679</v>
       </c>
       <c r="B7" t="n">
-        <v>56917</v>
+        <v>90155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,50 +1227,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760924</v>
+        <v>760876</v>
       </c>
       <c r="R7" t="n">
-        <v>7168506</v>
+        <v>7168516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701683</v>
+        <v>113701663</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1350,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1374,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761010</v>
+        <v>760896</v>
       </c>
       <c r="R8" t="n">
-        <v>7168418</v>
+        <v>7168483</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1548,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113701689</v>
+        <v>113701664</v>
       </c>
       <c r="B10" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,21 +1552,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1588,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760901</v>
+        <v>760841</v>
       </c>
       <c r="R10" t="n">
-        <v>7168493</v>
+        <v>7168507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1655,7 +1643,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701685</v>
+        <v>113701678</v>
       </c>
       <c r="B11" t="n">
         <v>81944</v>
@@ -1695,10 +1683,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760979</v>
+        <v>760891</v>
       </c>
       <c r="R11" t="n">
-        <v>7168521</v>
+        <v>7168581</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1762,7 +1750,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701700</v>
+        <v>113701662</v>
       </c>
       <c r="B12" t="n">
         <v>78201</v>
@@ -1802,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760847</v>
+        <v>760965</v>
       </c>
       <c r="R12" t="n">
-        <v>7168462</v>
+        <v>7168517</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1869,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113701680</v>
+        <v>113701684</v>
       </c>
       <c r="B13" t="n">
-        <v>77604</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1885,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1897,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760943</v>
+        <v>760985</v>
       </c>
       <c r="R13" t="n">
-        <v>7168426</v>
+        <v>7168457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,7 +1964,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113701662</v>
+        <v>113701683</v>
       </c>
       <c r="B14" t="n">
         <v>78201</v>
@@ -2016,10 +2004,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>760965</v>
+        <v>761010</v>
       </c>
       <c r="R14" t="n">
-        <v>7168517</v>
+        <v>7168418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2083,10 +2071,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113701659</v>
+        <v>113701680</v>
       </c>
       <c r="B15" t="n">
-        <v>56826</v>
+        <v>77604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,39 +2087,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760985</v>
+        <v>760943</v>
       </c>
       <c r="R15" t="n">
-        <v>7168527</v>
+        <v>7168426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2195,10 +2178,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113701679</v>
+        <v>113701686</v>
       </c>
       <c r="B16" t="n">
-        <v>90155</v>
+        <v>81944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2194,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2235,10 +2218,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760876</v>
+        <v>760976</v>
       </c>
       <c r="R16" t="n">
-        <v>7168516</v>
+        <v>7168520</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2302,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113701658</v>
+        <v>113701681</v>
       </c>
       <c r="B17" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,21 +2301,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2342,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761076</v>
+        <v>761131</v>
       </c>
       <c r="R17" t="n">
-        <v>7168434</v>
+        <v>7168392</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2409,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701664</v>
+        <v>113701685</v>
       </c>
       <c r="B18" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,21 +2408,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2449,10 +2432,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760841</v>
+        <v>760979</v>
       </c>
       <c r="R18" t="n">
-        <v>7168507</v>
+        <v>7168521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2516,10 +2499,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701678</v>
+        <v>113701659</v>
       </c>
       <c r="B19" t="n">
-        <v>81944</v>
+        <v>56826</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,34 +2515,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760891</v>
+        <v>760985</v>
       </c>
       <c r="R19" t="n">
-        <v>7168581</v>
+        <v>7168527</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113701663</v>
+        <v>113701701</v>
       </c>
       <c r="B20" t="n">
-        <v>90155</v>
+        <v>78201</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2663,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760896</v>
+        <v>760835</v>
       </c>
       <c r="R20" t="n">
-        <v>7168483</v>
+        <v>7168525</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2730,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113701701</v>
+        <v>113701689</v>
       </c>
       <c r="B21" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2770,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>760835</v>
+        <v>760901</v>
       </c>
       <c r="R21" t="n">
-        <v>7168525</v>
+        <v>7168493</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2837,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113701690</v>
+        <v>113701688</v>
       </c>
       <c r="B22" t="n">
-        <v>81944</v>
+        <v>56917</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2849,38 +2837,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1312</v>
+        <v>103031</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760880</v>
+        <v>760924</v>
       </c>
       <c r="R22" t="n">
-        <v>7168494</v>
+        <v>7168506</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2944,10 +2944,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113701681</v>
+        <v>113701690</v>
       </c>
       <c r="B23" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2960,21 +2960,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>761131</v>
+        <v>760880</v>
       </c>
       <c r="R23" t="n">
-        <v>7168392</v>
+        <v>7168494</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3051,10 +3051,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113701702</v>
+        <v>113701687</v>
       </c>
       <c r="B24" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,21 +3067,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>760873</v>
+        <v>760931</v>
       </c>
       <c r="R24" t="n">
-        <v>7168557</v>
+        <v>7168515</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -2392,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701685</v>
+        <v>113701659</v>
       </c>
       <c r="B18" t="n">
-        <v>81944</v>
+        <v>56826</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,34 +2408,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760979</v>
+        <v>760985</v>
       </c>
       <c r="R18" t="n">
-        <v>7168521</v>
+        <v>7168527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2499,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701659</v>
+        <v>113701685</v>
       </c>
       <c r="B19" t="n">
-        <v>56826</v>
+        <v>81944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2515,39 +2520,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760985</v>
+        <v>760979</v>
       </c>
       <c r="R19" t="n">
-        <v>7168527</v>
+        <v>7168521</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701700</v>
+        <v>113701678</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760847</v>
+        <v>760891</v>
       </c>
       <c r="R3" t="n">
-        <v>7168462</v>
+        <v>7168581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701682</v>
+        <v>113701663</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>90155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,25 +906,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761040</v>
+        <v>760896</v>
       </c>
       <c r="R4" t="n">
-        <v>7168409</v>
+        <v>7168483</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701702</v>
+        <v>113701687</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>90155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760873</v>
+        <v>760931</v>
       </c>
       <c r="R5" t="n">
-        <v>7168557</v>
+        <v>7168515</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701658</v>
+        <v>113701701</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,21 +1124,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1148,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761076</v>
+        <v>760835</v>
       </c>
       <c r="R6" t="n">
-        <v>7168434</v>
+        <v>7168525</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701679</v>
+        <v>113701681</v>
       </c>
       <c r="B7" t="n">
-        <v>90155</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760876</v>
+        <v>761131</v>
       </c>
       <c r="R7" t="n">
-        <v>7168516</v>
+        <v>7168392</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701663</v>
+        <v>113701702</v>
       </c>
       <c r="B8" t="n">
-        <v>90155</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760896</v>
+        <v>760873</v>
       </c>
       <c r="R8" t="n">
-        <v>7168483</v>
+        <v>7168557</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113701703</v>
+        <v>113701682</v>
       </c>
       <c r="B9" t="n">
-        <v>78201</v>
+        <v>79199</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1441,25 +1441,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760853</v>
+        <v>761040</v>
       </c>
       <c r="R9" t="n">
-        <v>7168609</v>
+        <v>7168409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113701664</v>
+        <v>113701659</v>
       </c>
       <c r="B10" t="n">
-        <v>78201</v>
+        <v>56826</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1552,34 +1552,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760841</v>
+        <v>760985</v>
       </c>
       <c r="R10" t="n">
-        <v>7168507</v>
+        <v>7168527</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1643,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701678</v>
+        <v>113701664</v>
       </c>
       <c r="B11" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,21 +1664,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1683,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760891</v>
+        <v>760841</v>
       </c>
       <c r="R11" t="n">
-        <v>7168581</v>
+        <v>7168507</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1750,7 +1755,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701662</v>
+        <v>113701703</v>
       </c>
       <c r="B12" t="n">
         <v>78201</v>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>760965</v>
+        <v>760853</v>
       </c>
       <c r="R12" t="n">
-        <v>7168517</v>
+        <v>7168609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113701684</v>
+        <v>113701658</v>
       </c>
       <c r="B13" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,21 +1878,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,10 +1902,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>760985</v>
+        <v>761076</v>
       </c>
       <c r="R13" t="n">
-        <v>7168457</v>
+        <v>7168434</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1964,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113701683</v>
+        <v>113701685</v>
       </c>
       <c r="B14" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1980,21 +1985,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761010</v>
+        <v>760979</v>
       </c>
       <c r="R14" t="n">
-        <v>7168418</v>
+        <v>7168521</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2071,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113701680</v>
+        <v>113701683</v>
       </c>
       <c r="B15" t="n">
-        <v>77604</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2087,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2111,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>760943</v>
+        <v>761010</v>
       </c>
       <c r="R15" t="n">
-        <v>7168426</v>
+        <v>7168418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2178,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113701686</v>
+        <v>113701684</v>
       </c>
       <c r="B16" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2194,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2218,10 +2223,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>760976</v>
+        <v>760985</v>
       </c>
       <c r="R16" t="n">
-        <v>7168520</v>
+        <v>7168457</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2285,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113701681</v>
+        <v>113701689</v>
       </c>
       <c r="B17" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2301,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>761131</v>
+        <v>760901</v>
       </c>
       <c r="R17" t="n">
-        <v>7168392</v>
+        <v>7168493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2392,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113701659</v>
+        <v>113701686</v>
       </c>
       <c r="B18" t="n">
-        <v>56826</v>
+        <v>81944</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,39 +2413,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>760985</v>
+        <v>760976</v>
       </c>
       <c r="R18" t="n">
-        <v>7168527</v>
+        <v>7168520</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2504,10 +2504,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113701685</v>
+        <v>113701700</v>
       </c>
       <c r="B19" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>760979</v>
+        <v>760847</v>
       </c>
       <c r="R19" t="n">
-        <v>7168521</v>
+        <v>7168462</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2611,10 +2611,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113701701</v>
+        <v>113701680</v>
       </c>
       <c r="B20" t="n">
-        <v>78201</v>
+        <v>77604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>760835</v>
+        <v>760943</v>
       </c>
       <c r="R20" t="n">
-        <v>7168525</v>
+        <v>7168426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113701689</v>
+        <v>113701662</v>
       </c>
       <c r="B21" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>760901</v>
+        <v>760965</v>
       </c>
       <c r="R21" t="n">
-        <v>7168493</v>
+        <v>7168517</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113701688</v>
+        <v>113701679</v>
       </c>
       <c r="B22" t="n">
-        <v>56917</v>
+        <v>90155</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,50 +2837,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103031</v>
+        <v>5442</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>760924</v>
+        <v>760876</v>
       </c>
       <c r="R22" t="n">
-        <v>7168506</v>
+        <v>7168516</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,10 +3039,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113701687</v>
+        <v>113701688</v>
       </c>
       <c r="B24" t="n">
-        <v>90155</v>
+        <v>56917</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3063,38 +3051,50 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>103031</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Dalfors, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>760931</v>
+        <v>760924</v>
       </c>
       <c r="R24" t="n">
-        <v>7168515</v>
+        <v>7168506</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 32605-2023 artfynd.xlsx
+++ b/artfynd/A 32605-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
